--- a/Data/input.xlsx
+++ b/Data/input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Work\Saheen sir\Keya Apu\Ecosystem Modeling\Submission - T &amp;F\1st Revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Work\Saheen sir\Keya Apu\Ecosystem Modeling\For Github\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C33CC3-B17B-4C5F-860C-F436CE1B84F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{9E6BEC46-195F-430C-A7F6-F1EC13D7260F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9E6BEC46-195F-430C-A7F6-F1EC13D7260F}"/>
   </bookViews>
   <sheets>
     <sheet name="calculated_data" sheetId="1" r:id="rId1"/>
@@ -547,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -586,19 +586,6 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
@@ -613,6 +600,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1029,17 +1028,17 @@
       <c r="K2" s="7">
         <v>0.52</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="19">
         <v>3.5928190000000004</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="19">
         <v>33.687570056359398</v>
       </c>
       <c r="N2">
         <f t="shared" ref="N2:N18" si="0">D2/J2</f>
         <v>1.8551908396946565E-2</v>
       </c>
-      <c r="O2" s="14">
+      <c r="O2" s="19">
         <f>SUM(N2:N6)</f>
         <v>0.22645393592543833</v>
       </c>
@@ -1076,13 +1075,13 @@
       <c r="K3" s="7">
         <v>0.59</v>
       </c>
-      <c r="L3" s="14"/>
-      <c r="M3" s="14"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
       <c r="N3">
         <f t="shared" si="0"/>
         <v>4.0549504950495051E-2</v>
       </c>
-      <c r="O3" s="14"/>
+      <c r="O3" s="19"/>
     </row>
     <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
@@ -1116,13 +1115,13 @@
       <c r="K4" s="7">
         <v>0.6</v>
       </c>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
       <c r="N4">
         <f t="shared" si="0"/>
         <v>1.0566964285714285E-2</v>
       </c>
-      <c r="O4" s="14"/>
+      <c r="O4" s="19"/>
     </row>
     <row r="5" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
@@ -1156,13 +1155,13 @@
       <c r="K5" s="7">
         <v>0.76</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
       <c r="N5">
         <f t="shared" si="0"/>
         <v>2.8672701149425286E-2</v>
       </c>
-      <c r="O5" s="14"/>
+      <c r="O5" s="19"/>
     </row>
     <row r="6" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
@@ -1196,13 +1195,13 @@
       <c r="K6" s="7">
         <v>0.38</v>
       </c>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
       <c r="N6">
         <f t="shared" si="0"/>
         <v>0.12811285714285714</v>
       </c>
-      <c r="O6" s="14"/>
+      <c r="O6" s="19"/>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
@@ -1238,17 +1237,17 @@
       <c r="K7" s="7">
         <v>0.49</v>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="20">
         <v>2.5258880000000006</v>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="20">
         <v>7.3968907666719312</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
         <v>3.129586776859504E-2</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="20">
         <f>SUM(N7:N8)</f>
         <v>3.4336123359649355E-2</v>
       </c>
@@ -1285,13 +1284,13 @@
       <c r="K8" s="7">
         <v>0.5</v>
       </c>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
       <c r="N8">
         <f t="shared" si="0"/>
         <v>3.0402555910543131E-3</v>
       </c>
-      <c r="O8" s="15"/>
+      <c r="O8" s="20"/>
     </row>
     <row r="9" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
@@ -1327,17 +1326,17 @@
       <c r="K9" s="7">
         <v>0.2</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9" s="21">
         <v>3.22871</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="21">
         <v>24.949115017890612</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
         <v>6.152916666666667E-2</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9" s="21">
         <f t="shared" ref="O9" si="1">SUM(N9:N10)</f>
         <v>0.54043259803921573</v>
       </c>
@@ -1374,13 +1373,13 @@
       <c r="K10" s="7">
         <v>0.63</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
       <c r="N10">
         <f t="shared" si="0"/>
         <v>0.47890343137254904</v>
       </c>
-      <c r="O10" s="16"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
@@ -1416,17 +1415,17 @@
       <c r="K11" s="7">
         <v>0.72</v>
       </c>
-      <c r="L11" s="15">
+      <c r="L11" s="20">
         <v>3.8456800000000002</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="20">
         <v>36.376322387464242</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
         <v>1.8382417647058826</v>
       </c>
-      <c r="O11" s="15">
+      <c r="O11" s="20">
         <f t="shared" ref="O11" si="2">SUM(N11:N12)</f>
         <v>5.8314335368577819</v>
       </c>
@@ -1463,13 +1462,13 @@
       <c r="K12" s="7">
         <v>0.54</v>
       </c>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
       <c r="N12">
         <f t="shared" si="0"/>
         <v>3.9931917721518988</v>
       </c>
-      <c r="O12" s="15"/>
+      <c r="O12" s="20"/>
     </row>
     <row r="13" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
@@ -1505,17 +1504,17 @@
       <c r="K13" s="7">
         <v>0.56000000000000005</v>
       </c>
-      <c r="L13" s="17">
+      <c r="L13" s="22">
         <v>3.6551269999999998</v>
       </c>
-      <c r="M13" s="17">
+      <c r="M13" s="22">
         <v>9.469223052076968</v>
       </c>
       <c r="N13">
         <f t="shared" si="0"/>
         <v>3.2354210526315791E-2</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="22">
         <f>SUM(N13:N15)</f>
         <v>8.1683263817851848E-2</v>
       </c>
@@ -1552,13 +1551,13 @@
       <c r="K14" s="7">
         <v>0.13</v>
       </c>
-      <c r="L14" s="17"/>
-      <c r="M14" s="17"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
       <c r="N14">
         <f t="shared" si="0"/>
         <v>3.2620689655172418E-2</v>
       </c>
-      <c r="O14" s="17"/>
+      <c r="O14" s="22"/>
     </row>
     <row r="15" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
@@ -1592,13 +1591,13 @@
       <c r="K15" s="7">
         <v>0.64</v>
       </c>
-      <c r="L15" s="17"/>
-      <c r="M15" s="17"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
       <c r="N15">
         <f t="shared" si="0"/>
         <v>1.6708363636363636E-2</v>
       </c>
-      <c r="O15" s="17"/>
+      <c r="O15" s="22"/>
     </row>
     <row r="16" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
@@ -1796,21 +1795,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="O2:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="O13:O15"/>
+    <mergeCell ref="L2:L6"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="L13:L15"/>
     <mergeCell ref="M2:M6"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="M11:M12"/>
     <mergeCell ref="M13:M15"/>
-    <mergeCell ref="L2:L6"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="L13:L15"/>
-    <mergeCell ref="O2:O6"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="O13:O15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2600,325 +2599,325 @@
     <col min="12" max="12" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="16" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="14">
         <v>2.0579999999999998</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="15">
         <v>0.22600000000000001</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="15">
         <v>3.593</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="15">
         <v>33.688000000000002</v>
       </c>
-      <c r="F2" s="19">
+      <c r="F2" s="14">
         <v>0.48899999999999999</v>
       </c>
-      <c r="G2" s="19">
+      <c r="G2" s="14">
         <v>0.107</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="19">
+      <c r="B3" s="14">
         <v>2.9780000000000002</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="15">
         <v>2.5259999999999998</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="15">
         <v>7.3970000000000002</v>
       </c>
-      <c r="F3" s="19">
+      <c r="F3" s="14">
         <v>0.71399999999999997</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="14">
         <v>0.34100000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="14">
         <v>2.286</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="15">
         <v>0.54</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="15">
         <v>3.2290000000000001</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>24.949000000000002</v>
       </c>
-      <c r="F4" s="19">
+      <c r="F4" s="14">
         <v>0.79700000000000004</v>
       </c>
-      <c r="G4" s="19">
+      <c r="G4" s="14">
         <v>0.129</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="14">
         <v>2.6320000000000001</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="15">
         <v>5.8310000000000004</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="15">
         <v>3.8460000000000001</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="15">
         <v>36.375999999999998</v>
       </c>
-      <c r="F5" s="19">
+      <c r="F5" s="14">
         <v>0.60399999999999998</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="14">
         <v>0.106</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="14">
         <v>3.2229999999999999</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="15">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="15">
         <v>3.6549999999999998</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="15">
         <v>9.4689999999999994</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="14">
         <v>0.51700000000000002</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="14">
         <v>0.38600000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="14">
         <v>2.0939999999999999</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="15">
         <v>0.27100000000000002</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="15">
         <v>1.39</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="15">
         <v>27.907</v>
       </c>
-      <c r="F7" s="19">
+      <c r="F7" s="14">
         <v>0.47599999999999998</v>
       </c>
-      <c r="G7" s="19">
+      <c r="G7" s="14">
         <v>0.05</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="19">
+      <c r="B8" s="14">
         <v>3.3330000000000002</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="15">
         <v>0.32900000000000001</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="15">
         <v>1.19</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="15">
         <v>8.4209999999999994</v>
       </c>
-      <c r="F8" s="19">
+      <c r="F8" s="14">
         <v>0.24099999999999999</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="14">
         <v>0.14099999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="14">
         <v>2.9580000000000002</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="14">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="15">
         <v>3.79</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="15">
         <v>14.186999999999999</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="15">
         <v>0.95</v>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="14">
         <v>0.26700000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="14">
         <v>2.6579999999999999</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="14">
         <v>0.39500000000000002</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="15">
         <v>3.16</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="15">
         <v>12.64</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="15">
         <v>0.95</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="14">
         <v>0.25</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="19">
+      <c r="B11" s="14">
         <v>2.1320000000000001</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="14">
         <v>0.66200000000000003</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="15">
         <v>4</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="15">
         <v>30</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="15">
         <v>0.95</v>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="14">
         <v>0.13300000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="14">
         <v>2.0529999999999999</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="14">
         <v>5.1619999999999999</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="15">
         <v>35</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="15">
         <v>140</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="15">
         <v>0.95</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="14">
         <v>0.25</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="14">
         <v>3.5449999999999999</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="15">
         <v>203</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="15">
         <v>0.95</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="G13" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="20">
+      <c r="B14" s="15">
         <v>1</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="15">
         <v>1</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="14">
         <v>0.51900000000000002</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="15" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2941,52 +2940,52 @@
     <col min="8" max="8" width="27.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="16" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="15">
         <v>1965.73</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="15">
         <v>1.23</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="15">
         <v>0.19500000000000001</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="15">
         <v>136.58000000000001</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="15">
         <v>0.26100000000000001</v>
       </c>
-      <c r="G2" s="20">
+      <c r="G2" s="15">
         <v>8.1</v>
       </c>
       <c r="H2" s="7" t="s">
@@ -2994,25 +2993,25 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="15">
         <v>6073.39</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>1.97</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="15">
         <v>0.19800000000000001</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="15">
         <v>1168.6400000000001</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="15">
         <v>0.30099999999999999</v>
       </c>
-      <c r="G3" s="20">
+      <c r="G3" s="15">
         <v>5.73</v>
       </c>
       <c r="H3" s="7" t="s">
@@ -3020,25 +3019,25 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="15">
         <v>5997.49</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="15">
         <v>2.0299999999999998</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="15">
         <v>0.16600000000000001</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>1207.55</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="15">
         <v>0.32100000000000001</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="15">
         <v>5.63</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -3046,25 +3045,25 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="15">
         <v>18217</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="15">
         <v>5.83</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="15">
         <v>6808.07</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H5" s="7" t="s">
@@ -3072,25 +3071,25 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="15">
         <v>0.19</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="15">
         <v>0.26400000000000001</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="15" t="s">
         <v>71</v>
       </c>
       <c r="H6" s="7" t="s">
@@ -3098,25 +3097,25 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="15">
         <v>3547.7</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="15">
         <v>1.6</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="15">
         <v>0.09</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="15">
         <v>0.504</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="15">
         <v>0.39</v>
       </c>
       <c r="H7" s="7" t="s">
@@ -3124,25 +3123,25 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="B8" s="20">
+      <c r="B8" s="15">
         <v>4435.96</v>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="15">
         <v>1.72</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="15">
         <v>0.11</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="15">
         <v>908.22</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="15">
         <v>0.25</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="15">
         <v>8.44</v>
       </c>
       <c r="H8" s="7" t="s">
@@ -3150,25 +3149,25 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="20">
+      <c r="B9" s="15">
         <v>38903</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="15">
         <v>10.36</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="15">
         <v>0.16</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="15">
         <v>15.33</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="15">
         <v>0.46800000000000003</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="15">
         <v>1.99</v>
       </c>
       <c r="H9" s="7" t="s">
@@ -3190,213 +3189,213 @@
     <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="16" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="22">
+      <c r="B2" s="17">
         <v>992.17</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="17">
         <v>136.58000000000001</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
+    <row r="4" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="17">
         <v>583.02</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+    <row r="5" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="17">
         <v>253.96</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B6" s="22">
+      <c r="B6" s="17">
         <v>2.6</v>
       </c>
-      <c r="C6" s="22"/>
-    </row>
-    <row r="7" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="22" t="s">
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="17">
         <v>1965.73</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="8" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+    <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="22">
+      <c r="B8" s="17">
         <v>930.32</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+    <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="17">
         <v>719.6</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+    <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="B10" s="22">
+      <c r="B10" s="17">
         <v>1.23</v>
       </c>
-      <c r="C10" s="22"/>
-    </row>
-    <row r="11" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="22" t="s">
+      <c r="C10" s="17"/>
+    </row>
+    <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="17">
         <v>136.58000000000001</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="22" t="s">
+    <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="B12" s="22">
+      <c r="B12" s="17">
         <v>42.14</v>
       </c>
-      <c r="C12" s="22"/>
-    </row>
-    <row r="13" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="22" t="s">
+      <c r="C12" s="17"/>
+    </row>
+    <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="B13" s="22">
+      <c r="B13" s="17">
         <v>8.9999999999999993E-3</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="14" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="22" t="s">
+    <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="22">
+      <c r="B14" s="17">
         <v>17.079999999999998</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="17" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="22" t="s">
+    <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="22">
+      <c r="B15" s="17">
         <v>0.41</v>
       </c>
-      <c r="C15" s="22"/>
-    </row>
-    <row r="16" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="22" t="s">
+      <c r="C15" s="17"/>
+    </row>
+    <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="22">
+      <c r="B16" s="17">
         <v>0.2</v>
       </c>
-      <c r="C16" s="22"/>
-    </row>
-    <row r="17" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="22" t="s">
+      <c r="C16" s="17"/>
+    </row>
+    <row r="17" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="22">
+      <c r="B17" s="17">
         <v>8.1</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="17" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="22" t="s">
+    <row r="18" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="B18" s="22">
+      <c r="B18" s="17">
         <v>26.1</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="17" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="22" t="s">
+    <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="17">
         <v>73.900000000000006</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="17" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:3" s="18" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="22" t="s">
+    <row r="20" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="22">
+      <c r="B20" s="17">
         <v>0.26100000000000001</v>
       </c>
-      <c r="C20" s="22"/>
+      <c r="C20" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3408,132 +3407,132 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="63.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="63.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="6.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="14" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="B3" s="20">
+      <c r="B3" s="15">
         <v>17.68</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="15">
         <v>8.68</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="15">
         <v>8.67</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="15">
         <v>8.7100000000000009</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="15">
         <v>17.75</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="15">
         <v>8.8000000000000007</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="15">
         <v>8.5</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="15">
         <v>8.6199999999999992</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="15">
         <v>17.690000000000001</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="15">
         <v>8.6999999999999993</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="15">
         <v>8.64</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="15">
         <v>8.69</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B6" s="20"/>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
     </row>
     <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="16" t="s">
         <v>126</v>
       </c>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
     </row>
     <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="B8" s="15"/>
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
     </row>
     <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="20"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
     </row>
     <row r="10" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3546,707 +3545,707 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="23" t="s">
+      <c r="D1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="23" t="s">
+      <c r="E1" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="23" t="s">
+      <c r="F1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="23" t="s">
+      <c r="G1" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="H1" s="23" t="s">
+      <c r="H1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="23" t="s">
+      <c r="I1" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="23" t="s">
+      <c r="J1" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="K1" s="23" t="s">
+      <c r="K1" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="23" t="s">
+      <c r="L1" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="23" t="s">
+      <c r="M1" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="23" t="s">
+      <c r="N1" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="O1" s="23" t="s">
+      <c r="O1" s="18" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="18">
         <v>-2.3900000000000001E-2</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="18">
         <v>-1.5299999999999999E-2</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="18">
         <v>-1.1900000000000001E-2</v>
       </c>
-      <c r="E2" s="23">
+      <c r="E2" s="18">
         <v>-1.2999999999999999E-2</v>
       </c>
-      <c r="F2" s="23">
+      <c r="F2" s="18">
         <v>2.52E-2</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="18">
         <v>-2.1100000000000001E-2</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="18">
         <v>-1.55E-2</v>
       </c>
-      <c r="I2" s="23">
+      <c r="I2" s="18">
         <v>-3.1800000000000002E-2</v>
       </c>
-      <c r="J2" s="23">
+      <c r="J2" s="18">
         <v>7.2700000000000004E-3</v>
       </c>
-      <c r="K2" s="23">
+      <c r="K2" s="18">
         <v>-6.8199999999999997E-3</v>
       </c>
-      <c r="L2" s="23">
+      <c r="L2" s="18">
         <v>5.4799999999999998E-4</v>
       </c>
-      <c r="M2" s="23">
+      <c r="M2" s="18">
         <v>-4.5900000000000003E-3</v>
       </c>
-      <c r="N2" s="23">
+      <c r="N2" s="18">
         <v>-2.1299999999999999E-2</v>
       </c>
-      <c r="O2" s="23">
+      <c r="O2" s="18">
         <v>1.1900000000000001E-2</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="18">
         <v>-7.0699999999999999E-3</v>
       </c>
-      <c r="C3" s="23">
+      <c r="C3" s="18">
         <v>-6.0400000000000002E-3</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="18">
         <v>-3.1E-2</v>
       </c>
-      <c r="E3" s="23">
+      <c r="E3" s="18">
         <v>-2.47E-3</v>
       </c>
-      <c r="F3" s="23">
+      <c r="F3" s="18">
         <v>2.8600000000000001E-3</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="18">
         <v>6.1600000000000001E-4</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="18">
         <v>-1.72E-3</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="18">
         <v>-7.3899999999999999E-3</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="18">
         <v>1.39E-3</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="18">
         <v>-4.9600000000000002E-4</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="18">
         <v>1.3500000000000001E-3</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="18">
         <v>-4.3600000000000003E-4</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="18">
         <v>-9.4399999999999996E-4</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="18">
         <v>-1.5100000000000001E-3</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="18">
         <v>-3.6499999999999998E-2</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="18">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="18">
         <v>-5.3600000000000002E-2</v>
       </c>
-      <c r="E4" s="23">
+      <c r="E4" s="18">
         <v>-3.2899999999999999E-2</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="18">
         <v>4.19E-2</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="18">
         <v>-4.8099999999999997E-2</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="18">
         <v>-1.9400000000000001E-2</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="18">
         <v>4.7899999999999998E-2</v>
       </c>
-      <c r="J4" s="23">
+      <c r="J4" s="18">
         <v>-3.6200000000000003E-2</v>
       </c>
-      <c r="K4" s="23">
+      <c r="K4" s="18">
         <v>-0.33100000000000002</v>
       </c>
-      <c r="L4" s="23">
+      <c r="L4" s="18">
         <v>7.6299999999999996E-3</v>
       </c>
-      <c r="M4" s="23">
+      <c r="M4" s="18">
         <v>-1.0699999999999999E-2</v>
       </c>
-      <c r="N4" s="23">
+      <c r="N4" s="18">
         <v>1.44E-2</v>
       </c>
-      <c r="O4" s="23">
+      <c r="O4" s="18">
         <v>3.5700000000000003E-2</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="18">
         <v>-0.25800000000000001</v>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="18">
         <v>-0.161</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="18">
         <v>-0.183</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="18">
         <v>-0.47299999999999998</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="18">
         <v>-9.0300000000000005E-2</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="18">
         <v>-0.26400000000000001</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="18">
         <v>-0.25</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="18">
         <v>0.11600000000000001</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="18">
         <v>0.184</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="18">
         <v>0.17799999999999999</v>
       </c>
-      <c r="L5" s="23">
+      <c r="L5" s="18">
         <v>-0.22500000000000001</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="18">
         <v>0.13300000000000001</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="18">
         <v>0.159</v>
       </c>
-      <c r="O5" s="23">
+      <c r="O5" s="18">
         <v>0.437</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="18">
         <v>-7.3999999999999996E-2</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="18">
         <v>-0.253</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="18">
         <v>-2.9399999999999999E-2</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="18">
         <v>-1.09E-2</v>
       </c>
-      <c r="F6" s="23">
+      <c r="F6" s="18">
         <v>-0.161</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="18">
         <v>-8.4400000000000003E-2</v>
       </c>
-      <c r="H6" s="23">
+      <c r="H6" s="18">
         <v>-1.0800000000000001E-2</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="18">
         <v>-0.746</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="18">
         <v>9.4500000000000001E-3</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="18">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="L6" s="23">
+      <c r="L6" s="18">
         <v>5.45E-3</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="18">
         <v>-2.16E-3</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="18">
         <v>-2.7299999999999998E-3</v>
       </c>
-      <c r="O6" s="23">
+      <c r="O6" s="18">
         <v>-8.3999999999999995E-3</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="18">
         <v>-9.7000000000000003E-3</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="18">
         <v>-1.9099999999999999E-2</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="18">
         <v>-8.0800000000000004E-3</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="18">
         <v>-6.4799999999999996E-3</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="18">
         <v>1.3299999999999999E-2</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="18">
         <v>-1.15E-2</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="18">
         <v>-1.8800000000000001E-2</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="18">
         <v>-2.5899999999999999E-2</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="18">
         <v>1.1299999999999999E-3</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="18">
         <v>-6.59E-2</v>
       </c>
-      <c r="L7" s="23">
+      <c r="L7" s="18">
         <v>-1.3699999999999999E-3</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="18">
         <v>-5.0499999999999998E-3</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="18">
         <v>-4.3E-3</v>
       </c>
-      <c r="O7" s="23">
+      <c r="O7" s="18">
         <v>4.47E-3</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="18">
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="18">
         <v>-7.1999999999999998E-3</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="18">
         <v>-0.14599999999999999</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="18">
         <v>-1.38E-2</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="18">
         <v>-7.0499999999999998E-3</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="18">
         <v>1.2699999999999999E-2</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="18">
         <v>-0.185</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="18">
         <v>-8.5299999999999994E-3</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="18">
         <v>-0.57099999999999995</v>
       </c>
-      <c r="K8" s="23">
+      <c r="K8" s="18">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="L8" s="23">
+      <c r="L8" s="18">
         <v>9.4800000000000006E-3</v>
       </c>
-      <c r="M8" s="23">
+      <c r="M8" s="18">
         <v>-4.3E-3</v>
       </c>
-      <c r="N8" s="23">
+      <c r="N8" s="18">
         <v>-1.17E-2</v>
       </c>
-      <c r="O8" s="23">
+      <c r="O8" s="18">
         <v>-1.67E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="18">
         <v>-4.6E-5</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="18">
         <v>-2.9799999999999998E-4</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="18">
         <v>-3.7599999999999998E-4</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="18">
         <v>-2.6999999999999999E-5</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="18">
         <v>8.2399999999999997E-4</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="18">
         <v>-5.8E-5</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="18">
         <v>-3.3000000000000003E-5</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="18">
         <v>-7.9199999999999995E-4</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="18">
         <v>-1.9999999999999999E-6</v>
       </c>
-      <c r="K9" s="23">
+      <c r="K9" s="18">
         <v>-4.3999999999999999E-5</v>
       </c>
-      <c r="L9" s="23">
+      <c r="L9" s="18">
         <v>1.5E-5</v>
       </c>
-      <c r="M9" s="23">
+      <c r="M9" s="18">
         <v>-5.0000000000000004E-6</v>
       </c>
-      <c r="N9" s="23">
+      <c r="N9" s="18">
         <v>-3.9999999999999998E-6</v>
       </c>
-      <c r="O9" s="23">
+      <c r="O9" s="18">
         <v>-3.8999999999999999E-5</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="18">
         <v>1.15E-2</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="18">
         <v>-3.09E-2</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="18">
         <v>-5.0700000000000002E-2</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="18">
         <v>-2.6700000000000001E-3</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="18">
         <v>1.73E-3</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="18">
         <v>1.98E-3</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="18">
         <v>0.19900000000000001</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="18">
         <v>-3.7699999999999997E-2</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="18">
         <v>-0.3</v>
       </c>
-      <c r="K10" s="23">
+      <c r="K10" s="18">
         <v>-0.251</v>
       </c>
-      <c r="L10" s="23">
+      <c r="L10" s="18">
         <v>1.31E-3</v>
       </c>
-      <c r="M10" s="23">
+      <c r="M10" s="18">
         <v>2.5999999999999998E-4</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="18">
         <v>1.8499999999999999E-2</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="18">
         <v>-4.3400000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="18">
         <v>-2.1000000000000001E-2</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="18">
         <v>9.1200000000000003E-2</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="18">
         <v>2.3400000000000001E-2</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="18">
         <v>-9.7599999999999996E-3</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="18">
         <v>-1.73E-3</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="18">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="18">
         <v>0.17100000000000001</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="18">
         <v>0.126</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="18">
         <v>8.8500000000000002E-3</v>
       </c>
-      <c r="K11" s="23">
+      <c r="K11" s="18">
         <v>-8.7099999999999997E-2</v>
       </c>
-      <c r="L11" s="23">
+      <c r="L11" s="18">
         <v>-1.24E-2</v>
       </c>
-      <c r="M11" s="23">
+      <c r="M11" s="18">
         <v>3.1800000000000001E-3</v>
       </c>
-      <c r="N11" s="23">
+      <c r="N11" s="18">
         <v>-6.8000000000000005E-2</v>
       </c>
-      <c r="O11" s="23">
+      <c r="O11" s="18">
         <v>-5.9500000000000004E-3</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="18">
         <v>-0.379</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="18">
         <v>-6.1499999999999999E-2</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="18">
         <v>-0.22800000000000001</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="18">
         <v>8.8099999999999998E-2</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="18">
         <v>-7.7399999999999997E-2</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="18">
         <v>-0.371</v>
       </c>
-      <c r="H12" s="23">
+      <c r="H12" s="18">
         <v>-5.67E-2</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="18">
         <v>4.5199999999999997E-2</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="18">
         <v>2.7400000000000001E-2</v>
       </c>
-      <c r="K12" s="23">
+      <c r="K12" s="18">
         <v>-0.16200000000000001</v>
       </c>
-      <c r="L12" s="23">
+      <c r="L12" s="18">
         <v>-0.51800000000000002</v>
       </c>
-      <c r="M12" s="23">
+      <c r="M12" s="18">
         <v>-0.40899999999999997</v>
       </c>
-      <c r="N12" s="23">
+      <c r="N12" s="18">
         <v>-0.371</v>
       </c>
-      <c r="O12" s="23">
+      <c r="O12" s="18">
         <v>4.6800000000000001E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="23">
+      <c r="B13" s="18">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="18">
         <v>-7.7299999999999994E-2</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="18">
         <v>0.307</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="18">
         <v>0.23</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="18">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="18">
         <v>0.254</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="18">
         <v>-1.6799999999999999E-2</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="18">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="18">
         <v>0.27600000000000002</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="18">
         <v>-0.11700000000000001</v>
       </c>
-      <c r="L13" s="23">
+      <c r="L13" s="18">
         <v>0.30399999999999999</v>
       </c>
-      <c r="M13" s="23">
+      <c r="M13" s="18">
         <v>-0.28899999999999998</v>
       </c>
-      <c r="N13" s="23">
+      <c r="N13" s="18">
         <v>-0.25900000000000001</v>
       </c>
-      <c r="O13" s="23">
+      <c r="O13" s="18">
         <v>0.22800000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="18">
         <v>0.29899999999999999</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="18">
         <v>0.26500000000000001</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="18">
         <v>5.2900000000000003E-2</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="18">
         <v>8.8199999999999997E-3</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="18">
         <v>5.7700000000000001E-2</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="18">
         <v>0.13100000000000001</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="18">
         <v>0.111</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="18">
         <v>0.121</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="18">
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="18">
         <v>0.43</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="18">
         <v>6.1499999999999999E-2</v>
       </c>
-      <c r="M14" s="23">
+      <c r="M14" s="18">
         <v>-6.0600000000000001E-2</v>
       </c>
-      <c r="N14" s="23">
+      <c r="N14" s="18">
         <v>0</v>
       </c>
-      <c r="O14" s="23">
+      <c r="O14" s="18">
         <v>2.23E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="23" t="s">
+      <c r="A15" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="23">
+      <c r="B15" s="18">
         <v>-0.54800000000000004</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="18">
         <v>-0.36799999999999999</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="18">
         <v>-0.30099999999999999</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="18">
         <v>-0.42399999999999999</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="18">
         <v>-0.61</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="18">
         <v>-0.53200000000000003</v>
       </c>
-      <c r="H15" s="23">
+      <c r="H15" s="18">
         <v>-0.50900000000000001</v>
       </c>
-      <c r="I15" s="23">
+      <c r="I15" s="18">
         <v>0.374</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="18">
         <v>0.39600000000000002</v>
       </c>
-      <c r="K15" s="23">
+      <c r="K15" s="18">
         <v>4.19E-2</v>
       </c>
-      <c r="L15" s="23">
+      <c r="L15" s="18">
         <v>0.189</v>
       </c>
-      <c r="M15" s="23">
+      <c r="M15" s="18">
         <v>-0.10100000000000001</v>
       </c>
-      <c r="N15" s="23">
+      <c r="N15" s="18">
         <v>-0.121</v>
       </c>
-      <c r="O15" s="23">
+      <c r="O15" s="18">
         <v>-0.42199999999999999</v>
       </c>
     </row>
